--- a/templates/BNY12748 - template.xlsx
+++ b/templates/BNY12748 - template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$12:$H$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$12:$H$45</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1268,8 +1268,8 @@
     <col width="5.42578125" customWidth="1" style="56" min="9" max="9"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="56" min="10" max="10"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="56" min="11" max="11"/>
-    <col width="9.140625" customWidth="1" style="56" min="12" max="25"/>
-    <col width="9.140625" customWidth="1" style="56" min="26" max="16384"/>
+    <col width="9.140625" customWidth="1" style="56" min="12" max="26"/>
+    <col width="9.140625" customWidth="1" style="56" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1426,14 +1426,14 @@
       <c r="A21" s="3" t="n"/>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C21" s="35" t="n">
-        <v>1.19046762</v>
+        <v>1.19415808</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>-0.0009757053005449157</v>
+        <v>-0.0004156431386366233</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>0.0005426623598601132</v>
@@ -1442,10 +1442,10 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>-1.797997010141687</v>
+        <v>-0.7659332383837478</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>-1.675980020982006</v>
+        <v>-0.7139549163299508</v>
       </c>
       <c r="I21" s="3" t="n"/>
     </row>
@@ -1453,14 +1453,14 @@
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>1.1916303</v>
+        <v>1.19465463</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.0004604217392607524</v>
+        <v>3.176751223676888e-05</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>0.0005426623598601132</v>
@@ -1469,10 +1469,10 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>0.8484497420816863</v>
+        <v>0.05854010631022551</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>0.7908716246553639</v>
+        <v>0.05456741476692953</v>
       </c>
       <c r="I22" s="3" t="n"/>
     </row>
@@ -1480,14 +1480,14 @@
       <c r="A23" s="3" t="n"/>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1.1910819</v>
+        <v>1.19461668</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>0.0003257679947510361</v>
+        <v>0.001845362320795019</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>0.0005426623598601132</v>
@@ -1496,10 +1496,10 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0.6003143369571683</v>
+        <v>3.400571805405324</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>0.5595753660179833</v>
+        <v>3.169799712472778</v>
       </c>
       <c r="I23" s="3" t="n"/>
     </row>
@@ -1507,14 +1507,14 @@
       <c r="A24" s="3" t="n"/>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1.19069401</v>
+        <v>1.19241624</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>0.0006288942639616213</v>
+        <v>-0.001590860068945155</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>0.0005426623598601132</v>
@@ -1523,10 +1523,10 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>1.158905261318911</v>
+        <v>-2.931583589757809</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>1.080258784205858</v>
+        <v>-2.732638318394989</v>
       </c>
       <c r="I24" s="3" t="n"/>
     </row>
@@ -1534,14 +1534,14 @@
       <c r="A25" s="3" t="n"/>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>1.18994566</v>
+        <v>1.19431623</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>0.001829550584755646</v>
+        <v>0.0003632853286377191</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>0.0005426623598601132</v>
@@ -1550,10 +1550,10 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>3.37143446843681</v>
+        <v>0.6694500217987596</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>3.142639714792915</v>
+        <v>0.6240193144104696</v>
       </c>
       <c r="I25" s="3" t="n"/>
     </row>
@@ -1607,24 +1607,24 @@
       <c r="A28" s="3" t="n"/>
       <c r="B28" s="38" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr"/>
       <c r="D28" s="18" t="n">
-        <v>-0.0005487770313363782</v>
+        <v>0.00187420479945466</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>0.01124174012968759</v>
+        <v>0.004082314319127534</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>-0.05234740012045368</v>
+        <v>0.4925861729516547</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>-0.04881602180850525</v>
+        <v>0.459103501823253</v>
       </c>
       <c r="I28" s="20" t="n"/>
     </row>
@@ -1637,19 +1637,19 @@
       </c>
       <c r="C29" s="42" t="inlineStr"/>
       <c r="D29" s="43" t="n">
-        <v>0.0008439180675872127</v>
+        <v>0.002553722084065235</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F29" s="43" t="n">
-        <v>0.01243701403980046</v>
+        <v>0.01234950728397388</v>
       </c>
       <c r="G29" s="44" t="n">
-        <v>0.0727650124121822</v>
+        <v>0.2218617477384957</v>
       </c>
       <c r="H29" s="44" t="n">
-        <v>0.06785536020836977</v>
+        <v>0.2067873661145359</v>
       </c>
       <c r="I29" s="45" t="n"/>
     </row>
@@ -1662,19 +1662,19 @@
       </c>
       <c r="C30" s="42" t="inlineStr"/>
       <c r="D30" s="43" t="n">
-        <v>0.0246844284211174</v>
+        <v>0.02482438882059124</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F30" s="43" t="n">
-        <v>0.03786670851308371</v>
+        <v>0.03777700382293214</v>
       </c>
       <c r="G30" s="44" t="n">
-        <v>0.6995106567031112</v>
+        <v>0.705265248191144</v>
       </c>
       <c r="H30" s="44" t="n">
-        <v>0.6518767907326413</v>
+        <v>0.6571296373038945</v>
       </c>
       <c r="I30" s="45" t="n"/>
     </row>
@@ -1687,19 +1687,19 @@
       </c>
       <c r="C31" s="42" t="inlineStr"/>
       <c r="D31" s="43" t="n">
-        <v>0.06454949123702147</v>
+        <v>0.05863814781075405</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F31" s="43" t="n">
-        <v>0.07721385841335238</v>
+        <v>0.07712075287811992</v>
       </c>
       <c r="G31" s="44" t="n">
-        <v>0.8981692147593255</v>
+        <v>0.8169693949384677</v>
       </c>
       <c r="H31" s="44" t="n">
-        <v>0.8359832362147455</v>
+        <v>0.7603420042258222</v>
       </c>
       <c r="I31" s="45" t="n"/>
     </row>
@@ -1712,19 +1712,19 @@
       </c>
       <c r="C32" s="42" t="inlineStr"/>
       <c r="D32" s="43" t="n">
-        <v>0.1795399256985561</v>
+        <v>0.1725058713510501</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F32" s="43" t="n">
-        <v>0.1592951134207572</v>
+        <v>0.1594961966253503</v>
       </c>
       <c r="G32" s="44" t="n">
-        <v>1.214609914555671</v>
+        <v>1.165453931254295</v>
       </c>
       <c r="H32" s="44" t="n">
-        <v>1.127089976855253</v>
+        <v>1.081567303803858</v>
       </c>
       <c r="I32" s="45" t="n"/>
     </row>
@@ -1737,19 +1737,19 @@
       </c>
       <c r="C33" s="42" t="inlineStr"/>
       <c r="D33" s="43" t="n">
-        <v>0.02305130924481125</v>
+        <v>0.0262227772220045</v>
       </c>
       <c r="E33" s="43" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F33" s="43" t="n">
-        <v>0.03480618036515426</v>
+        <v>0.04084631843637321</v>
       </c>
       <c r="G33" s="44" t="n">
-        <v>0.7106042588490978</v>
+        <v>0.6890687802186081</v>
       </c>
       <c r="H33" s="44" t="n">
-        <v>0.6622763257265872</v>
+        <v>0.6419863093133358</v>
       </c>
       <c r="I33" s="45" t="n"/>
     </row>
@@ -1787,24 +1787,24 @@
       </c>
       <c r="C35" s="42" t="inlineStr"/>
       <c r="D35" s="43" t="n">
-        <v>0.1904676199999999</v>
+        <v>0.19415808</v>
       </c>
       <c r="E35" s="43" t="n">
-        <v>0.1598571421810462</v>
+        <v>0.166166642673091</v>
       </c>
       <c r="F35" s="43" t="n">
-        <v>0.172427480766582</v>
+        <v>0.1792709109631645</v>
       </c>
       <c r="G35" s="44" t="n">
-        <v>1.191486457228704</v>
+        <v>1.168454010243067</v>
       </c>
       <c r="H35" s="44" t="n">
-        <v>1.104624501577212</v>
+        <v>1.083042859306351</v>
       </c>
       <c r="I35" s="45" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37" ht="26.1" customHeight="1">
+    <row r="36" ht="15.95" customHeight="1"/>
+    <row r="37">
       <c r="B37" s="39" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
@@ -1818,7 +1818,7 @@
       <c r="H37" s="39" t="n"/>
       <c r="I37" s="3" t="n"/>
     </row>
-    <row r="38" ht="15.95" customHeight="1">
+    <row r="38" ht="26.1" customHeight="1">
       <c r="B38" s="22" t="inlineStr">
         <is>
           <t>Hoje¹</t>
@@ -1827,7 +1827,7 @@
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="46" t="n">
-        <v>2688093.46</v>
+        <v>2685656.75</v>
       </c>
       <c r="F38" s="41" t="n"/>
       <c r="G38" s="41" t="n"/>
@@ -1843,7 +1843,7 @@
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="46" t="n">
-        <v>2053033.690753968</v>
+        <v>2118811.049722222</v>
       </c>
       <c r="F39" s="41" t="n"/>
       <c r="G39" s="41" t="n"/>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C41" s="36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D41" s="28" t="n"/>
@@ -1909,7 +1909,7 @@
       <c r="H43" s="30" t="n"/>
       <c r="I43" s="3" t="n"/>
     </row>
-    <row r="44" ht="43.5" customHeight="1">
+    <row r="44" ht="15.95" customHeight="1">
       <c r="A44" s="3" t="n"/>
       <c r="B44" s="40" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
       <c r="H44" s="40" t="n"/>
       <c r="I44" s="3" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="43.5" customHeight="1">
       <c r="A45" s="3" t="n"/>
       <c r="B45" s="55" t="n"/>
       <c r="I45" s="3" t="n"/>
@@ -1932,12 +1932,6 @@
     <row r="46">
       <c r="A46" s="3" t="n"/>
       <c r="B46" s="31" t="n"/>
-      <c r="C46" s="31" t="n"/>
-      <c r="D46" s="31" t="n"/>
-      <c r="E46" s="31" t="n"/>
-      <c r="F46" s="31" t="n"/>
-      <c r="G46" s="31" t="n"/>
-      <c r="H46" s="31" t="n"/>
       <c r="I46" s="3" t="n"/>
     </row>
     <row r="47">
@@ -1962,11 +1956,11 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="B8:H13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="87"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="85"/>
 </worksheet>
 </file>